--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A3BCA2-1E7A-4F25-B3A5-95BC27DF149D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84416B2-B93D-4819-9C72-5370FEB19DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>No regular classes. Preparing for CA1 at home and relaxed.</t>
+  </si>
+  <si>
+    <t>Had a CA today. Attended classes and revised the important topics at home.</t>
   </si>
 </sst>
 </file>
@@ -2244,27 +2247,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="14">
+        <v>240</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>420</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84416B2-B93D-4819-9C72-5370FEB19DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E152087-CAA2-4EAE-B654-31876E3041C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Had a CA today. Attended classes and revised the important topics at home.</t>
+  </si>
+  <si>
+    <t>Had regular classes and preparing for DBMS CA1 at home.</t>
   </si>
 </sst>
 </file>
@@ -2293,27 +2296,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>300</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E152087-CAA2-4EAE-B654-31876E3041C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6456FF6-2906-4687-AB12-E2ACCA8D47FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Had regular classes and preparing for DBMS CA1 at home.</t>
+  </si>
+  <si>
+    <t>Had regular classes.</t>
   </si>
 </sst>
 </file>
@@ -2343,26 +2346,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>360</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6456FF6-2906-4687-AB12-E2ACCA8D47FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3965D332-A7AD-444A-A29B-00821820AF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>Had regular classes.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attend Fresher's Party. </t>
   </si>
 </sst>
 </file>
@@ -2392,26 +2398,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="14">
+        <v>240</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>90</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>950</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3965D332-A7AD-444A-A29B-00821820AF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F7F53C-603D-4F82-87D7-85760D678E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2443,27 +2443,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F7F53C-603D-4F82-87D7-85760D678E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E73299-DD79-4FF5-9301-3CFFF122C0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t xml:space="preserve">Attend Fresher's Party. </t>
+  </si>
+  <si>
+    <t>No classes today. Studied at home, watched movie and relaxed.</t>
   </si>
 </sst>
 </file>
@@ -2489,27 +2492,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E73299-DD79-4FF5-9301-3CFFF122C0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EE193F-6031-4BDE-9F5D-33C6CF734174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2538,27 +2538,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>40</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EE193F-6031-4BDE-9F5D-33C6CF734174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EE62D0-7149-4BF3-B92A-81A93FEB4D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>No classes today. Studied at home, watched movie and relaxed.</t>
+  </si>
+  <si>
+    <t>Had classes and preparing for Python CA1 at home.</t>
   </si>
 </sst>
 </file>
@@ -2584,27 +2587,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B39" s="14">
+        <v>360</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>150</v>
+      </c>
+      <c r="G39" s="14">
+        <v>3</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EE62D0-7149-4BF3-B92A-81A93FEB4D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DD968A-3E56-483E-A82A-87D740B9584A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Had classes and preparing for Python CA1 at home.</t>
+  </si>
+  <si>
+    <t>Had classes and give Python CA1 at home through Online.</t>
   </si>
 </sst>
 </file>
@@ -2633,27 +2636,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DD968A-3E56-483E-A82A-87D740B9584A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD7BACA-CA24-46E5-BE45-C301041BFCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Had classes and give Python CA1 at home through Online.</t>
+  </si>
+  <si>
+    <t>Had classes and some classes was exempted and solving maths at home.</t>
   </si>
 </sst>
 </file>
@@ -2682,27 +2685,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B41" s="14">
+        <v>540</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD7BACA-CA24-46E5-BE45-C301041BFCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15544EC-E9DD-4F87-B823-17CFFAF5D521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Had classes and some classes was exempted and solving maths at home.</t>
+  </si>
+  <si>
+    <t>Had regular classes and preparing  for Analytical skill CA1 at night.</t>
   </si>
 </sst>
 </file>
@@ -2731,27 +2734,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15544EC-E9DD-4F87-B823-17CFFAF5D521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9FA949-98D9-469D-9B75-5AC089F5015D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2780,27 +2780,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9FA949-98D9-469D-9B75-5AC089F5015D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B557075-F196-4851-AEE6-CFA91D51034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Had regular classes and preparing  for Analytical skill CA1 at night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No classes today. Had an Analytical Skills test, and overall it was a good day. </t>
   </si>
 </sst>
 </file>
@@ -2826,27 +2829,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>40</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>90</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>770</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B557075-F196-4851-AEE6-CFA91D51034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DFF431-46DC-4155-9A03-D02A1D0C03E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,9 +207,6 @@
     <t>MCA/D1P2635</t>
   </si>
   <si>
-    <t>Mostly relaxed today with a short study session.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 2026-08-17</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
   </si>
   <si>
     <t>Stressed</t>
-  </si>
-  <si>
-    <t>Busy college day, but managed some revision.</t>
   </si>
   <si>
     <t>Had regular classes and completed a little study at night.</t>
@@ -951,7 +945,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -1015,7 +1009,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1107,11 +1101,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I67" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J67" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1129,99 +1123,99 @@
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B7" s="14">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C7" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D7" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E7" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F7" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>985</v>
+        <v>720</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>455</v>
+        <v>720</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B8" s="14">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C8" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D8" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E8" s="14">
+        <v>45</v>
+      </c>
+      <c r="F8" s="14">
         <v>0</v>
       </c>
-      <c r="F8" s="14">
-        <v>300</v>
-      </c>
       <c r="G8" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
         <v>60</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>765</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>675</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N8" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>46249</v>
+      <c r="A9" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="B9" s="14">
         <v>480</v>
@@ -1230,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="14">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E9" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F9" s="14">
         <v>0</v>
@@ -1246,293 +1240,293 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>825</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>615</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>62</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B10" s="14">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="C10" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D10" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
         <v>45</v>
-      </c>
-      <c r="F10" s="14">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0</v>
-      </c>
-      <c r="H10" s="14">
-        <v>60</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>765</v>
+        <v>855</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>675</v>
+        <v>585</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46253</v>
       </c>
       <c r="B11" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C11" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="E11" s="14">
         <v>45</v>
       </c>
       <c r="F11" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11" s="14">
         <v>60</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>1055</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>385</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B12" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E12" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F12" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G12" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H12" s="14">
         <v>45</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>745</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>695</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B13" s="14">
         <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E13" s="14">
         <v>45</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1055</v>
+        <v>950</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>385</v>
+        <v>490</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C14" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D14" s="14">
+        <v>300</v>
+      </c>
+      <c r="E14" s="14">
         <v>60</v>
       </c>
-      <c r="E14" s="14">
+      <c r="F14" s="14">
         <v>0</v>
       </c>
-      <c r="F14" s="14">
-        <v>200</v>
-      </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>695</v>
+        <v>540</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B15" s="14">
         <v>420</v>
       </c>
       <c r="C15" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D15" s="14">
         <v>120</v>
       </c>
       <c r="E15" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>630</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>810</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>51</v>
@@ -1543,329 +1537,329 @@
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B16" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
         <v>0</v>
       </c>
-      <c r="D16" s="14">
-        <v>300</v>
-      </c>
-      <c r="E16" s="14">
-        <v>60</v>
-      </c>
       <c r="F16" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G16" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>705</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>735</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B17" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C17" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D17" s="14">
         <v>120</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>880</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>560</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B18" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C18" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F18" s="14">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
         <v>45</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>705</v>
+        <v>950</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>490</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B19" s="14">
         <v>360</v>
       </c>
       <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>90</v>
+      </c>
+      <c r="E19" s="14">
         <v>0</v>
       </c>
-      <c r="D19" s="14">
-        <v>120</v>
-      </c>
-      <c r="E19" s="14">
-        <v>60</v>
-      </c>
       <c r="F19" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H19" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>760</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B20" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D20" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E20" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>640</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M20" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N20" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B21" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
       </c>
       <c r="D21" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E21" s="14">
         <v>0</v>
       </c>
       <c r="F21" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G21" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>690</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="K21" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N21" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B22" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
         <v>0</v>
       </c>
-      <c r="D22" s="14">
-        <v>120</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="F22" s="14">
-        <v>200</v>
-      </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
       <c r="H22" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B23" s="14">
         <v>420</v>
@@ -1874,50 +1868,50 @@
         <v>30</v>
       </c>
       <c r="D23" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F23" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G23" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>810</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>630</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B24" s="14">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="C24" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
         <v>180</v>
@@ -1926,38 +1920,38 @@
         <v>30</v>
       </c>
       <c r="F24" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>795</v>
+        <v>960</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>645</v>
+        <v>480</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B25" s="14">
         <v>420</v>
@@ -1966,56 +1960,56 @@
         <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E25" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H25" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B26" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C26" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D26" s="14">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E26" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>300</v>
@@ -2024,176 +2018,176 @@
         <v>6</v>
       </c>
       <c r="H26" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1125</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>315</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B27" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C27" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D27" s="14">
         <v>180</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F27" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>60</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>875</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>565</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
         <v>420</v>
-      </c>
-      <c r="C28" s="14">
-        <v>45</v>
-      </c>
-      <c r="D28" s="14">
-        <v>240</v>
       </c>
       <c r="E28" s="14">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1125</v>
+        <v>960</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>315</v>
+        <v>480</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B29" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C29" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D29" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E29" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>875</v>
+        <v>720</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>565</v>
+        <v>720</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M29" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B30" s="14">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="C30" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D30" s="14">
         <v>420</v>
@@ -2202,73 +2196,73 @@
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G30" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="14">
         <v>60</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="L30" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B31" s="14">
         <v>300</v>
       </c>
       <c r="C31" s="14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D31" s="14">
         <v>300</v>
       </c>
       <c r="E31" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F31" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G31" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>1120</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>320</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>51</v>
@@ -2277,153 +2271,153 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B32" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="C32" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D32" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="E32" s="14">
         <v>0</v>
       </c>
       <c r="F32" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G32" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H32" s="14">
         <v>60</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1040</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B33" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
       </c>
       <c r="D33" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="E33" s="14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F33" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>490</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>950</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B34" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C34" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D34" s="14">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="E34" s="14">
         <v>0</v>
       </c>
       <c r="F34" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G34" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H34" s="14">
         <v>60</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>890</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B35" s="14">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="C35" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D35" s="14">
         <v>120</v>
@@ -2438,81 +2432,81 @@
         <v>0</v>
       </c>
       <c r="H35" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>490</v>
+        <v>750</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>690</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N35" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="M35" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B36" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C36" s="14">
         <v>40</v>
       </c>
       <c r="D36" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E36" s="14">
         <v>0</v>
       </c>
       <c r="F36" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G36" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>820</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B37" s="14">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="C37" s="14">
         <v>30</v>
@@ -2524,73 +2518,73 @@
         <v>0</v>
       </c>
       <c r="F37" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G37" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B38" s="14">
         <v>420</v>
       </c>
       <c r="C38" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D38" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E38" s="14">
         <v>0</v>
       </c>
       <c r="F38" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G38" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H38" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>990</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>450</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
         <v>51</v>
@@ -2599,12 +2593,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B39" s="14">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="C39" s="14">
         <v>30</v>
@@ -2616,27 +2610,27 @@
         <v>0</v>
       </c>
       <c r="F39" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G39" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" s="14">
         <v>60</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>950</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>490</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
         <v>51</v>
@@ -2645,9 +2639,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B40" s="14">
         <v>420</v>
@@ -2656,10 +2650,10 @@
         <v>30</v>
       </c>
       <c r="D40" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E40" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F40" s="14">
         <v>300</v>
@@ -2668,18 +2662,18 @@
         <v>6</v>
       </c>
       <c r="H40" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>50</v>
@@ -2693,187 +2687,139 @@
     </row>
     <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B41" s="14">
-        <v>540</v>
+        <v>420</v>
       </c>
       <c r="C41" s="14">
         <v>30</v>
       </c>
       <c r="D41" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E41" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F41" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G41" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H41" s="14">
         <v>60</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1020</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="B42" s="14">
         <v>420</v>
       </c>
       <c r="C42" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D42" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E42" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F42" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H42" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>670</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>770</v>
       </c>
       <c r="K42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M42" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L42" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N42" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="13">
-        <v>46283</v>
-      </c>
-      <c r="B43" s="14">
-        <v>420</v>
-      </c>
-      <c r="C43" s="14">
-        <v>30</v>
-      </c>
-      <c r="D43" s="14">
-        <v>180</v>
-      </c>
-      <c r="E43" s="14">
-        <v>30</v>
-      </c>
-      <c r="F43" s="14">
-        <v>300</v>
-      </c>
-      <c r="G43" s="14">
-        <v>6</v>
-      </c>
-      <c r="H43" s="14">
-        <v>60</v>
-      </c>
-      <c r="I43" s="15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="J43" s="15">
+        <v/>
+      </c>
+      <c r="J43" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L43" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M43" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N43" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="13">
-        <v>46284</v>
-      </c>
-      <c r="B44" s="14">
-        <v>420</v>
-      </c>
-      <c r="C44" s="14">
-        <v>40</v>
-      </c>
-      <c r="D44" s="14">
-        <v>120</v>
-      </c>
-      <c r="E44" s="14">
-        <v>0</v>
-      </c>
-      <c r="F44" s="14">
-        <v>0</v>
-      </c>
-      <c r="G44" s="14">
-        <v>0</v>
-      </c>
-      <c r="H44" s="14">
-        <v>90</v>
-      </c>
-      <c r="I44" s="15">
+        <v/>
+      </c>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="17"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>670</v>
-      </c>
-      <c r="J44" s="15">
+        <v/>
+      </c>
+      <c r="J44" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>770</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L44" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>87</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
@@ -3391,11 +3337,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I68:I131" si="2">IF(SUM(B68:F68,H68)=0,"",SUM(B68:F68,H68))</f>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J68:J131" si="3">IF(I68="","",1440-I68)</f>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3413,11 +3359,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3435,11 +3381,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -4799,11 +4745,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I132:I195" si="4">IF(SUM(B132:F132,H132)=0,"",SUM(B132:F132,H132))</f>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J132:J195" si="5">IF(I132="","",1440-I132)</f>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4821,11 +4767,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4843,11 +4789,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -6207,11 +6153,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I196:I259" si="6">IF(SUM(B196:F196,H196)=0,"",SUM(B196:F196,H196))</f>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J196:J259" si="7">IF(I196="","",1440-I196)</f>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6229,11 +6175,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6251,11 +6197,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -7615,11 +7561,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I260:I323" si="8">IF(SUM(B260:F260,H260)=0,"",SUM(B260:F260,H260))</f>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J260:J323" si="9">IF(I260="","",1440-I260)</f>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7637,11 +7583,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7659,11 +7605,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -9023,11 +8969,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I324:I387" si="10">IF(SUM(B324:F324,H324)=0,"",SUM(B324:F324,H324))</f>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J324:J387" si="11">IF(I324="","",1440-I324)</f>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9045,11 +8991,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9067,11 +9013,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -10431,11 +10377,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I388:I399" si="12">IF(SUM(B388:F388,H388)=0,"",SUM(B388:F388,H388))</f>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J388:J399" si="13">IF(I388="","",1440-I388)</f>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10453,11 +10399,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10475,11 +10421,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10685,50 +10631,6 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10738,21 +10640,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J399">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L399" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M399" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
